--- a/model/data/games.xlsx
+++ b/model/data/games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S540"/>
+  <dimension ref="A1:S556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34482,6 +34482,990 @@
         <v>0</v>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>22400509</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>20250108/OKCCLE</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="E541" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="F541" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G541" t="n">
+        <v>129</v>
+      </c>
+      <c r="H541" t="n">
+        <v>122</v>
+      </c>
+      <c r="I541" t="n">
+        <v>36</v>
+      </c>
+      <c r="J541" t="n">
+        <v>35</v>
+      </c>
+      <c r="K541" t="n">
+        <v>40</v>
+      </c>
+      <c r="L541" t="n">
+        <v>38</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="R541" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="S541" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>22400510</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>20250108/CHIIND</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>1610612754</v>
+      </c>
+      <c r="E542" t="n">
+        <v>1610612741</v>
+      </c>
+      <c r="F542" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G542" t="n">
+        <v>129</v>
+      </c>
+      <c r="H542" t="n">
+        <v>113</v>
+      </c>
+      <c r="I542" t="n">
+        <v>37</v>
+      </c>
+      <c r="J542" t="n">
+        <v>23</v>
+      </c>
+      <c r="K542" t="n">
+        <v>46</v>
+      </c>
+      <c r="L542" t="n">
+        <v>39</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N542" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P542" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="R542" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="S542" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>22400512</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>20250108/WASPHI</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1610612764</v>
+      </c>
+      <c r="F543" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G543" t="n">
+        <v>109</v>
+      </c>
+      <c r="H543" t="n">
+        <v>103</v>
+      </c>
+      <c r="I543" t="n">
+        <v>21</v>
+      </c>
+      <c r="J543" t="n">
+        <v>26</v>
+      </c>
+      <c r="K543" t="n">
+        <v>36</v>
+      </c>
+      <c r="L543" t="n">
+        <v>51</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N543" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="P543" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="R543" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="S543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>22400511</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>20250108/TORNYK</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>1610612752</v>
+      </c>
+      <c r="E544" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="F544" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G544" t="n">
+        <v>112</v>
+      </c>
+      <c r="H544" t="n">
+        <v>98</v>
+      </c>
+      <c r="I544" t="n">
+        <v>24</v>
+      </c>
+      <c r="J544" t="n">
+        <v>25</v>
+      </c>
+      <c r="K544" t="n">
+        <v>43</v>
+      </c>
+      <c r="L544" t="n">
+        <v>33</v>
+      </c>
+      <c r="M544" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="N544" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P544" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R544" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="S544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>22400513</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>20250108/DETBKN</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="F545" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G545" t="n">
+        <v>98</v>
+      </c>
+      <c r="H545" t="n">
+        <v>113</v>
+      </c>
+      <c r="I545" t="n">
+        <v>24</v>
+      </c>
+      <c r="J545" t="n">
+        <v>30</v>
+      </c>
+      <c r="K545" t="n">
+        <v>38</v>
+      </c>
+      <c r="L545" t="n">
+        <v>42</v>
+      </c>
+      <c r="M545" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="N545" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R545" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>22400514</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>20250108/PORNOP</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>1610612740</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1610612757</v>
+      </c>
+      <c r="F546" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G546" t="n">
+        <v>100</v>
+      </c>
+      <c r="H546" t="n">
+        <v>119</v>
+      </c>
+      <c r="I546" t="n">
+        <v>19</v>
+      </c>
+      <c r="J546" t="n">
+        <v>24</v>
+      </c>
+      <c r="K546" t="n">
+        <v>41</v>
+      </c>
+      <c r="L546" t="n">
+        <v>44</v>
+      </c>
+      <c r="M546" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="N546" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="P546" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="R546" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="S546" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>22400515</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>20250108/LACDEN</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="E547" t="n">
+        <v>1610612746</v>
+      </c>
+      <c r="F547" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G547" t="n">
+        <v>126</v>
+      </c>
+      <c r="H547" t="n">
+        <v>103</v>
+      </c>
+      <c r="I547" t="n">
+        <v>29</v>
+      </c>
+      <c r="J547" t="n">
+        <v>14</v>
+      </c>
+      <c r="K547" t="n">
+        <v>45</v>
+      </c>
+      <c r="L547" t="n">
+        <v>40</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="N547" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="P547" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="R547" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="S547" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2025-01-08T00:00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>22400516</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>20250108/SASMIL</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>1610612749</v>
+      </c>
+      <c r="E548" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="F548" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G548" t="n">
+        <v>121</v>
+      </c>
+      <c r="H548" t="n">
+        <v>105</v>
+      </c>
+      <c r="I548" t="n">
+        <v>26</v>
+      </c>
+      <c r="J548" t="n">
+        <v>24</v>
+      </c>
+      <c r="K548" t="n">
+        <v>57</v>
+      </c>
+      <c r="L548" t="n">
+        <v>46</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="N548" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P548" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="R548" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="S548" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>22400517</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>20250109/TORCLE</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="E549" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="F549" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G549" t="n">
+        <v>132</v>
+      </c>
+      <c r="H549" t="n">
+        <v>126</v>
+      </c>
+      <c r="I549" t="n">
+        <v>31</v>
+      </c>
+      <c r="J549" t="n">
+        <v>34</v>
+      </c>
+      <c r="K549" t="n">
+        <v>42</v>
+      </c>
+      <c r="L549" t="n">
+        <v>37</v>
+      </c>
+      <c r="M549" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="N549" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P549" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R549" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="S549" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>22400518</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>20250109/GSWDET</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="E550" t="n">
+        <v>1610612744</v>
+      </c>
+      <c r="F550" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G550" t="n">
+        <v>104</v>
+      </c>
+      <c r="H550" t="n">
+        <v>107</v>
+      </c>
+      <c r="I550" t="n">
+        <v>25</v>
+      </c>
+      <c r="J550" t="n">
+        <v>32</v>
+      </c>
+      <c r="K550" t="n">
+        <v>40</v>
+      </c>
+      <c r="L550" t="n">
+        <v>49</v>
+      </c>
+      <c r="M550" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="N550" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R550" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="S550" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>22400519</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>20250109/MINORL</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="F551" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G551" t="n">
+        <v>89</v>
+      </c>
+      <c r="H551" t="n">
+        <v>104</v>
+      </c>
+      <c r="I551" t="n">
+        <v>21</v>
+      </c>
+      <c r="J551" t="n">
+        <v>21</v>
+      </c>
+      <c r="K551" t="n">
+        <v>47</v>
+      </c>
+      <c r="L551" t="n">
+        <v>50</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="N551" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="P551" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R551" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="S551" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>22400521</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>20250109/PORDAL</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>1610612742</v>
+      </c>
+      <c r="E552" t="n">
+        <v>1610612757</v>
+      </c>
+      <c r="F552" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G552" t="n">
+        <v>117</v>
+      </c>
+      <c r="H552" t="n">
+        <v>111</v>
+      </c>
+      <c r="I552" t="n">
+        <v>26</v>
+      </c>
+      <c r="J552" t="n">
+        <v>24</v>
+      </c>
+      <c r="K552" t="n">
+        <v>53</v>
+      </c>
+      <c r="L552" t="n">
+        <v>43</v>
+      </c>
+      <c r="M552" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N552" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P552" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R552" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="S552" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>22400520</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>20250109/HOUMEM</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>1610612763</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1610612745</v>
+      </c>
+      <c r="F553" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G553" t="n">
+        <v>115</v>
+      </c>
+      <c r="H553" t="n">
+        <v>119</v>
+      </c>
+      <c r="I553" t="n">
+        <v>20</v>
+      </c>
+      <c r="J553" t="n">
+        <v>21</v>
+      </c>
+      <c r="K553" t="n">
+        <v>43</v>
+      </c>
+      <c r="L553" t="n">
+        <v>44</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N553" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="O553" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P553" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="S553" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>22400522</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>20250109/ATLPHX</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>1610612756</v>
+      </c>
+      <c r="E554" t="n">
+        <v>1610612737</v>
+      </c>
+      <c r="F554" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G554" t="n">
+        <v>123</v>
+      </c>
+      <c r="H554" t="n">
+        <v>115</v>
+      </c>
+      <c r="I554" t="n">
+        <v>33</v>
+      </c>
+      <c r="J554" t="n">
+        <v>32</v>
+      </c>
+      <c r="K554" t="n">
+        <v>42</v>
+      </c>
+      <c r="L554" t="n">
+        <v>32</v>
+      </c>
+      <c r="M554" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="O554" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P554" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="R554" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="S554" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>22400523</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>20250109/MIAUTA</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>1610612762</v>
+      </c>
+      <c r="E555" t="n">
+        <v>1610612748</v>
+      </c>
+      <c r="F555" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G555" t="n">
+        <v>92</v>
+      </c>
+      <c r="H555" t="n">
+        <v>97</v>
+      </c>
+      <c r="I555" t="n">
+        <v>20</v>
+      </c>
+      <c r="J555" t="n">
+        <v>26</v>
+      </c>
+      <c r="K555" t="n">
+        <v>49</v>
+      </c>
+      <c r="L555" t="n">
+        <v>49</v>
+      </c>
+      <c r="M555" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="N555" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="O555" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="P555" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="R555" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S555" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2025-01-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>22400524</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>20250109/CHALAL</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>1610612747</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="F556" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+      <c r="J556" t="inlineStr"/>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
+      <c r="N556" t="inlineStr"/>
+      <c r="O556" t="inlineStr"/>
+      <c r="P556" t="inlineStr"/>
+      <c r="Q556" t="inlineStr"/>
+      <c r="R556" t="inlineStr"/>
+      <c r="S556" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/model/data/games.xlsx
+++ b/model/data/games.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\NBA_MODELO\NBA_prevision\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A401C5F8-4B1E-4839-9351-A7E94EC56E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D59581-E3D1-441A-9EBA-03808582EB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="687">
   <si>
     <t>GAME_DATE_EST</t>
   </si>
@@ -1967,6 +1967,120 @@
   </si>
   <si>
     <t>20250109/MIAUTA</t>
+  </si>
+  <si>
+    <t>2025-01-10T00:00:00</t>
+  </si>
+  <si>
+    <t>20250110/GSWIND</t>
+  </si>
+  <si>
+    <t>20250110/MILORL</t>
+  </si>
+  <si>
+    <t>20250110/NOPPHI</t>
+  </si>
+  <si>
+    <t>20250110/SACBOS</t>
+  </si>
+  <si>
+    <t>20250110/OKCNYK</t>
+  </si>
+  <si>
+    <t>20250110/WASCHI</t>
+  </si>
+  <si>
+    <t>20250110/BKNDEN</t>
+  </si>
+  <si>
+    <t>2025-01-11T00:00:00</t>
+  </si>
+  <si>
+    <t>20250111/UTAPHX</t>
+  </si>
+  <si>
+    <t>20250111/TORDET</t>
+  </si>
+  <si>
+    <t>20250111/MEMMIN</t>
+  </si>
+  <si>
+    <t>20250111/MIAPOR</t>
+  </si>
+  <si>
+    <t>2025-01-12T00:00:00</t>
+  </si>
+  <si>
+    <t>20250112/MILNYK</t>
+  </si>
+  <si>
+    <t>20250112/DENDAL</t>
+  </si>
+  <si>
+    <t>20250112/SACCHI</t>
+  </si>
+  <si>
+    <t>20250112/NOPBOS</t>
+  </si>
+  <si>
+    <t>20250112/INDCLE</t>
+  </si>
+  <si>
+    <t>20250112/PHIORL</t>
+  </si>
+  <si>
+    <t>20250112/OKCWAS</t>
+  </si>
+  <si>
+    <t>20250112/BKNUTA</t>
+  </si>
+  <si>
+    <t>20250112/CHAPHX</t>
+  </si>
+  <si>
+    <t>2025-01-13T00:00:00</t>
+  </si>
+  <si>
+    <t>20250113/MINWAS</t>
+  </si>
+  <si>
+    <t>20250113/DETNYK</t>
+  </si>
+  <si>
+    <t>20250113/GSWTOR</t>
+  </si>
+  <si>
+    <t>20250113/MEMHOU</t>
+  </si>
+  <si>
+    <t>20250113/SASLAL</t>
+  </si>
+  <si>
+    <t>20250113/MIALAC</t>
+  </si>
+  <si>
+    <t>2025-01-14T00:00:00</t>
+  </si>
+  <si>
+    <t>20250114/CLEIND</t>
+  </si>
+  <si>
+    <t>20250114/OKCPHI</t>
+  </si>
+  <si>
+    <t>20250114/PHXATL</t>
+  </si>
+  <si>
+    <t>20250114/NOPCHI</t>
+  </si>
+  <si>
+    <t>20250114/SACMIL</t>
+  </si>
+  <si>
+    <t>20250114/DENDAL</t>
+  </si>
+  <si>
+    <t>20250114/BKNPOR</t>
   </si>
 </sst>
 </file>
@@ -2329,11 +2443,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S555"/>
+  <dimension ref="A1:S588"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -35081,6 +35195,1953 @@
         <v>0</v>
       </c>
     </row>
+    <row r="556" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>649</v>
+      </c>
+      <c r="B556">
+        <v>22400525</v>
+      </c>
+      <c r="C556" t="s">
+        <v>650</v>
+      </c>
+      <c r="D556">
+        <v>1610612754</v>
+      </c>
+      <c r="E556">
+        <v>1610612744</v>
+      </c>
+      <c r="F556">
+        <v>2024</v>
+      </c>
+      <c r="G556">
+        <v>108</v>
+      </c>
+      <c r="H556">
+        <v>96</v>
+      </c>
+      <c r="I556">
+        <v>27</v>
+      </c>
+      <c r="J556">
+        <v>25</v>
+      </c>
+      <c r="K556">
+        <v>48</v>
+      </c>
+      <c r="L556">
+        <v>42</v>
+      </c>
+      <c r="M556">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="N556">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="O556">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="P556">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="Q556">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="R556">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="S556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>649</v>
+      </c>
+      <c r="B557">
+        <v>22400526</v>
+      </c>
+      <c r="C557" t="s">
+        <v>651</v>
+      </c>
+      <c r="D557">
+        <v>1610612753</v>
+      </c>
+      <c r="E557">
+        <v>1610612749</v>
+      </c>
+      <c r="F557">
+        <v>2024</v>
+      </c>
+      <c r="G557">
+        <v>106</v>
+      </c>
+      <c r="H557">
+        <v>109</v>
+      </c>
+      <c r="I557">
+        <v>20</v>
+      </c>
+      <c r="J557">
+        <v>18</v>
+      </c>
+      <c r="K557">
+        <v>44</v>
+      </c>
+      <c r="L557">
+        <v>43</v>
+      </c>
+      <c r="M557">
+        <v>0.43</v>
+      </c>
+      <c r="N557">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="O557">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="P557">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q557">
+        <v>0.35</v>
+      </c>
+      <c r="R557">
+        <v>0.36</v>
+      </c>
+      <c r="S557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>649</v>
+      </c>
+      <c r="B558">
+        <v>22400527</v>
+      </c>
+      <c r="C558" t="s">
+        <v>652</v>
+      </c>
+      <c r="D558">
+        <v>1610612755</v>
+      </c>
+      <c r="E558">
+        <v>1610612740</v>
+      </c>
+      <c r="F558">
+        <v>2024</v>
+      </c>
+      <c r="G558">
+        <v>115</v>
+      </c>
+      <c r="H558">
+        <v>123</v>
+      </c>
+      <c r="I558">
+        <v>23</v>
+      </c>
+      <c r="J558">
+        <v>31</v>
+      </c>
+      <c r="K558">
+        <v>42</v>
+      </c>
+      <c r="L558">
+        <v>44</v>
+      </c>
+      <c r="M558">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="N558">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="O558">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="P558">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="Q558">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="R558">
+        <v>0.45</v>
+      </c>
+      <c r="S558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>649</v>
+      </c>
+      <c r="B559">
+        <v>22400528</v>
+      </c>
+      <c r="C559" t="s">
+        <v>653</v>
+      </c>
+      <c r="D559">
+        <v>1610612738</v>
+      </c>
+      <c r="E559">
+        <v>1610612758</v>
+      </c>
+      <c r="F559">
+        <v>2024</v>
+      </c>
+      <c r="G559">
+        <v>97</v>
+      </c>
+      <c r="H559">
+        <v>114</v>
+      </c>
+      <c r="I559">
+        <v>22</v>
+      </c>
+      <c r="J559">
+        <v>26</v>
+      </c>
+      <c r="K559">
+        <v>43</v>
+      </c>
+      <c r="L559">
+        <v>56</v>
+      </c>
+      <c r="M559">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="N559">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="O559">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="P559">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="Q559">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="R559">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>649</v>
+      </c>
+      <c r="B560">
+        <v>22400529</v>
+      </c>
+      <c r="C560" t="s">
+        <v>654</v>
+      </c>
+      <c r="D560">
+        <v>1610612752</v>
+      </c>
+      <c r="E560">
+        <v>1610612760</v>
+      </c>
+      <c r="F560">
+        <v>2024</v>
+      </c>
+      <c r="G560">
+        <v>101</v>
+      </c>
+      <c r="H560">
+        <v>126</v>
+      </c>
+      <c r="I560">
+        <v>18</v>
+      </c>
+      <c r="J560">
+        <v>20</v>
+      </c>
+      <c r="K560">
+        <v>43</v>
+      </c>
+      <c r="L560">
+        <v>46</v>
+      </c>
+      <c r="M560">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="N560">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="O560">
+        <v>1</v>
+      </c>
+      <c r="P560">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="Q560">
+        <v>0.129</v>
+      </c>
+      <c r="R560">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="S560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>649</v>
+      </c>
+      <c r="B561">
+        <v>22400530</v>
+      </c>
+      <c r="C561" t="s">
+        <v>655</v>
+      </c>
+      <c r="D561">
+        <v>1610612741</v>
+      </c>
+      <c r="E561">
+        <v>1610612764</v>
+      </c>
+      <c r="F561">
+        <v>2024</v>
+      </c>
+      <c r="G561">
+        <v>138</v>
+      </c>
+      <c r="H561">
+        <v>105</v>
+      </c>
+      <c r="I561">
+        <v>39</v>
+      </c>
+      <c r="J561">
+        <v>26</v>
+      </c>
+      <c r="K561">
+        <v>55</v>
+      </c>
+      <c r="L561">
+        <v>45</v>
+      </c>
+      <c r="M561">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="N561">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="O561">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="P561">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q561">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="R561">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="S561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>649</v>
+      </c>
+      <c r="B562">
+        <v>22400531</v>
+      </c>
+      <c r="C562" t="s">
+        <v>656</v>
+      </c>
+      <c r="D562">
+        <v>1610612743</v>
+      </c>
+      <c r="E562">
+        <v>1610612751</v>
+      </c>
+      <c r="F562">
+        <v>2024</v>
+      </c>
+      <c r="G562">
+        <v>124</v>
+      </c>
+      <c r="H562">
+        <v>105</v>
+      </c>
+      <c r="I562">
+        <v>34</v>
+      </c>
+      <c r="J562">
+        <v>26</v>
+      </c>
+      <c r="K562">
+        <v>49</v>
+      </c>
+      <c r="L562">
+        <v>39</v>
+      </c>
+      <c r="M562">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="N562">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="O562">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="P562">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="Q562">
+        <v>0.375</v>
+      </c>
+      <c r="R562">
+        <v>0.311</v>
+      </c>
+      <c r="S562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>657</v>
+      </c>
+      <c r="B563">
+        <v>22400533</v>
+      </c>
+      <c r="C563" t="s">
+        <v>658</v>
+      </c>
+      <c r="D563">
+        <v>1610612756</v>
+      </c>
+      <c r="E563">
+        <v>1610612762</v>
+      </c>
+      <c r="F563">
+        <v>2024</v>
+      </c>
+      <c r="G563">
+        <v>114</v>
+      </c>
+      <c r="H563">
+        <v>106</v>
+      </c>
+      <c r="I563">
+        <v>26</v>
+      </c>
+      <c r="J563">
+        <v>26</v>
+      </c>
+      <c r="K563">
+        <v>38</v>
+      </c>
+      <c r="L563">
+        <v>50</v>
+      </c>
+      <c r="M563">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="N563">
+        <v>0.438</v>
+      </c>
+      <c r="O563">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="P563">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="Q563">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="R563">
+        <v>0.214</v>
+      </c>
+      <c r="S563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>657</v>
+      </c>
+      <c r="B564">
+        <v>22400534</v>
+      </c>
+      <c r="C564" t="s">
+        <v>659</v>
+      </c>
+      <c r="D564">
+        <v>1610612765</v>
+      </c>
+      <c r="E564">
+        <v>1610612761</v>
+      </c>
+      <c r="F564">
+        <v>2024</v>
+      </c>
+      <c r="G564">
+        <v>123</v>
+      </c>
+      <c r="H564">
+        <v>114</v>
+      </c>
+      <c r="I564">
+        <v>35</v>
+      </c>
+      <c r="J564">
+        <v>27</v>
+      </c>
+      <c r="K564">
+        <v>46</v>
+      </c>
+      <c r="L564">
+        <v>45</v>
+      </c>
+      <c r="M564">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="N564">
+        <v>0.435</v>
+      </c>
+      <c r="O564">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="P564">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q564">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="R564">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="S564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>657</v>
+      </c>
+      <c r="B565">
+        <v>22400535</v>
+      </c>
+      <c r="C565" t="s">
+        <v>660</v>
+      </c>
+      <c r="D565">
+        <v>1610612750</v>
+      </c>
+      <c r="E565">
+        <v>1610612763</v>
+      </c>
+      <c r="F565">
+        <v>2024</v>
+      </c>
+      <c r="G565">
+        <v>125</v>
+      </c>
+      <c r="H565">
+        <v>127</v>
+      </c>
+      <c r="I565">
+        <v>37</v>
+      </c>
+      <c r="J565">
+        <v>25</v>
+      </c>
+      <c r="K565">
+        <v>41</v>
+      </c>
+      <c r="L565">
+        <v>46</v>
+      </c>
+      <c r="M565">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="N565">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="O565">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="P565">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="Q565">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="R565">
+        <v>0.39</v>
+      </c>
+      <c r="S565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>657</v>
+      </c>
+      <c r="B566">
+        <v>22400536</v>
+      </c>
+      <c r="C566" t="s">
+        <v>661</v>
+      </c>
+      <c r="D566">
+        <v>1610612757</v>
+      </c>
+      <c r="E566">
+        <v>1610612748</v>
+      </c>
+      <c r="F566">
+        <v>2024</v>
+      </c>
+      <c r="G566">
+        <v>98</v>
+      </c>
+      <c r="H566">
+        <v>119</v>
+      </c>
+      <c r="I566">
+        <v>24</v>
+      </c>
+      <c r="J566">
+        <v>31</v>
+      </c>
+      <c r="K566">
+        <v>51</v>
+      </c>
+      <c r="L566">
+        <v>43</v>
+      </c>
+      <c r="M566">
+        <v>0.379</v>
+      </c>
+      <c r="N566">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="O566">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="P566">
+        <v>0.75</v>
+      </c>
+      <c r="Q566">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="R566">
+        <v>0.432</v>
+      </c>
+      <c r="S566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>662</v>
+      </c>
+      <c r="B567">
+        <v>22400539</v>
+      </c>
+      <c r="C567" t="s">
+        <v>663</v>
+      </c>
+      <c r="D567">
+        <v>1610612752</v>
+      </c>
+      <c r="E567">
+        <v>1610612749</v>
+      </c>
+      <c r="F567">
+        <v>2024</v>
+      </c>
+      <c r="G567">
+        <v>140</v>
+      </c>
+      <c r="H567">
+        <v>106</v>
+      </c>
+      <c r="I567">
+        <v>29</v>
+      </c>
+      <c r="J567">
+        <v>22</v>
+      </c>
+      <c r="K567">
+        <v>49</v>
+      </c>
+      <c r="L567">
+        <v>39</v>
+      </c>
+      <c r="M567">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N567">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="O567">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="P567">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="Q567">
+        <v>0.439</v>
+      </c>
+      <c r="R567">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="S567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>662</v>
+      </c>
+      <c r="B568">
+        <v>22400540</v>
+      </c>
+      <c r="C568" t="s">
+        <v>664</v>
+      </c>
+      <c r="D568">
+        <v>1610612742</v>
+      </c>
+      <c r="E568">
+        <v>1610612743</v>
+      </c>
+      <c r="F568">
+        <v>2024</v>
+      </c>
+      <c r="G568">
+        <v>101</v>
+      </c>
+      <c r="H568">
+        <v>112</v>
+      </c>
+      <c r="I568">
+        <v>27</v>
+      </c>
+      <c r="J568">
+        <v>23</v>
+      </c>
+      <c r="K568">
+        <v>37</v>
+      </c>
+      <c r="L568">
+        <v>55</v>
+      </c>
+      <c r="M568">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="N568">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="O568">
+        <v>0.76</v>
+      </c>
+      <c r="P568">
+        <v>0.65</v>
+      </c>
+      <c r="Q568">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="R568">
+        <v>0.219</v>
+      </c>
+      <c r="S568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>662</v>
+      </c>
+      <c r="B569">
+        <v>22400541</v>
+      </c>
+      <c r="C569" t="s">
+        <v>665</v>
+      </c>
+      <c r="D569">
+        <v>1610612741</v>
+      </c>
+      <c r="E569">
+        <v>1610612758</v>
+      </c>
+      <c r="F569">
+        <v>2024</v>
+      </c>
+      <c r="G569">
+        <v>119</v>
+      </c>
+      <c r="H569">
+        <v>124</v>
+      </c>
+      <c r="I569">
+        <v>26</v>
+      </c>
+      <c r="J569">
+        <v>33</v>
+      </c>
+      <c r="K569">
+        <v>45</v>
+      </c>
+      <c r="L569">
+        <v>53</v>
+      </c>
+      <c r="M569">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="N569">
+        <v>0.495</v>
+      </c>
+      <c r="O569">
+        <v>0.75</v>
+      </c>
+      <c r="P569">
+        <v>0.81</v>
+      </c>
+      <c r="Q569">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="R569">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="S569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>662</v>
+      </c>
+      <c r="B570">
+        <v>22400542</v>
+      </c>
+      <c r="C570" t="s">
+        <v>666</v>
+      </c>
+      <c r="D570">
+        <v>1610612738</v>
+      </c>
+      <c r="E570">
+        <v>1610612740</v>
+      </c>
+      <c r="F570">
+        <v>2024</v>
+      </c>
+      <c r="G570">
+        <v>120</v>
+      </c>
+      <c r="H570">
+        <v>119</v>
+      </c>
+      <c r="I570">
+        <v>23</v>
+      </c>
+      <c r="J570">
+        <v>24</v>
+      </c>
+      <c r="K570">
+        <v>55</v>
+      </c>
+      <c r="L570">
+        <v>42</v>
+      </c>
+      <c r="M570">
+        <v>0.436</v>
+      </c>
+      <c r="N570">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="O570">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="P570">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="Q570">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="R570">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="S570">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>662</v>
+      </c>
+      <c r="B571">
+        <v>22400543</v>
+      </c>
+      <c r="C571" t="s">
+        <v>667</v>
+      </c>
+      <c r="D571">
+        <v>1610612739</v>
+      </c>
+      <c r="E571">
+        <v>1610612754</v>
+      </c>
+      <c r="F571">
+        <v>2024</v>
+      </c>
+      <c r="G571">
+        <v>93</v>
+      </c>
+      <c r="H571">
+        <v>108</v>
+      </c>
+      <c r="I571">
+        <v>24</v>
+      </c>
+      <c r="J571">
+        <v>30</v>
+      </c>
+      <c r="K571">
+        <v>44</v>
+      </c>
+      <c r="L571">
+        <v>50</v>
+      </c>
+      <c r="M571">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="N571">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="O571">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="P571">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="Q571">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="R571">
+        <v>0.314</v>
+      </c>
+      <c r="S571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>662</v>
+      </c>
+      <c r="B572">
+        <v>22400544</v>
+      </c>
+      <c r="C572" t="s">
+        <v>668</v>
+      </c>
+      <c r="D572">
+        <v>1610612753</v>
+      </c>
+      <c r="E572">
+        <v>1610612755</v>
+      </c>
+      <c r="F572">
+        <v>2024</v>
+      </c>
+      <c r="G572">
+        <v>104</v>
+      </c>
+      <c r="H572">
+        <v>99</v>
+      </c>
+      <c r="I572">
+        <v>23</v>
+      </c>
+      <c r="J572">
+        <v>17</v>
+      </c>
+      <c r="K572">
+        <v>41</v>
+      </c>
+      <c r="L572">
+        <v>29</v>
+      </c>
+      <c r="M572">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="N572">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="O572">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="P572">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="Q572">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="R572">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="S572">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>662</v>
+      </c>
+      <c r="B573">
+        <v>22400545</v>
+      </c>
+      <c r="C573" t="s">
+        <v>669</v>
+      </c>
+      <c r="D573">
+        <v>1610612764</v>
+      </c>
+      <c r="E573">
+        <v>1610612760</v>
+      </c>
+      <c r="F573">
+        <v>2024</v>
+      </c>
+      <c r="G573">
+        <v>95</v>
+      </c>
+      <c r="H573">
+        <v>136</v>
+      </c>
+      <c r="I573">
+        <v>20</v>
+      </c>
+      <c r="J573">
+        <v>26</v>
+      </c>
+      <c r="K573">
+        <v>39</v>
+      </c>
+      <c r="L573">
+        <v>56</v>
+      </c>
+      <c r="M573">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="N573">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="O573">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="P573">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="Q573">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="R573">
+        <v>0.371</v>
+      </c>
+      <c r="S573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>662</v>
+      </c>
+      <c r="B574">
+        <v>22400546</v>
+      </c>
+      <c r="C574" t="s">
+        <v>670</v>
+      </c>
+      <c r="D574">
+        <v>1610612762</v>
+      </c>
+      <c r="E574">
+        <v>1610612751</v>
+      </c>
+      <c r="F574">
+        <v>2024</v>
+      </c>
+      <c r="G574">
+        <v>112</v>
+      </c>
+      <c r="H574">
+        <v>111</v>
+      </c>
+      <c r="I574">
+        <v>25</v>
+      </c>
+      <c r="J574">
+        <v>26</v>
+      </c>
+      <c r="K574">
+        <v>41</v>
+      </c>
+      <c r="L574">
+        <v>54</v>
+      </c>
+      <c r="M574">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="N574">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="O574">
+        <v>0.75</v>
+      </c>
+      <c r="P574">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="Q574">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="R574">
+        <v>0.25</v>
+      </c>
+      <c r="S574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>662</v>
+      </c>
+      <c r="B575">
+        <v>22400547</v>
+      </c>
+      <c r="C575" t="s">
+        <v>671</v>
+      </c>
+      <c r="D575">
+        <v>1610612756</v>
+      </c>
+      <c r="E575">
+        <v>1610612766</v>
+      </c>
+      <c r="F575">
+        <v>2024</v>
+      </c>
+      <c r="G575">
+        <v>120</v>
+      </c>
+      <c r="H575">
+        <v>113</v>
+      </c>
+      <c r="I575">
+        <v>31</v>
+      </c>
+      <c r="J575">
+        <v>30</v>
+      </c>
+      <c r="K575">
+        <v>39</v>
+      </c>
+      <c r="L575">
+        <v>52</v>
+      </c>
+      <c r="M575">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="N575">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="O575">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="P575">
+        <v>0.8</v>
+      </c>
+      <c r="Q575">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="R575">
+        <v>0.375</v>
+      </c>
+      <c r="S575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>672</v>
+      </c>
+      <c r="B576">
+        <v>22400548</v>
+      </c>
+      <c r="C576" t="s">
+        <v>673</v>
+      </c>
+      <c r="D576">
+        <v>1610612764</v>
+      </c>
+      <c r="E576">
+        <v>1610612750</v>
+      </c>
+      <c r="F576">
+        <v>2024</v>
+      </c>
+      <c r="G576">
+        <v>106</v>
+      </c>
+      <c r="H576">
+        <v>120</v>
+      </c>
+      <c r="I576">
+        <v>27</v>
+      </c>
+      <c r="J576">
+        <v>20</v>
+      </c>
+      <c r="K576">
+        <v>34</v>
+      </c>
+      <c r="L576">
+        <v>53</v>
+      </c>
+      <c r="M576">
+        <v>0.44</v>
+      </c>
+      <c r="N576">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="O576">
+        <v>0.6</v>
+      </c>
+      <c r="P576">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="Q576">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="R576">
+        <v>0.378</v>
+      </c>
+      <c r="S576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>672</v>
+      </c>
+      <c r="B577">
+        <v>22400549</v>
+      </c>
+      <c r="C577" t="s">
+        <v>674</v>
+      </c>
+      <c r="D577">
+        <v>1610612752</v>
+      </c>
+      <c r="E577">
+        <v>1610612765</v>
+      </c>
+      <c r="F577">
+        <v>2024</v>
+      </c>
+      <c r="G577">
+        <v>119</v>
+      </c>
+      <c r="H577">
+        <v>124</v>
+      </c>
+      <c r="I577">
+        <v>26</v>
+      </c>
+      <c r="J577">
+        <v>20</v>
+      </c>
+      <c r="K577">
+        <v>42</v>
+      </c>
+      <c r="L577">
+        <v>39</v>
+      </c>
+      <c r="M577">
+        <v>0.5</v>
+      </c>
+      <c r="N577">
+        <v>0.5</v>
+      </c>
+      <c r="O577">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="P577">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="Q577">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="R577">
+        <v>0.441</v>
+      </c>
+      <c r="S577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>672</v>
+      </c>
+      <c r="B578">
+        <v>22400550</v>
+      </c>
+      <c r="C578" t="s">
+        <v>675</v>
+      </c>
+      <c r="D578">
+        <v>1610612761</v>
+      </c>
+      <c r="E578">
+        <v>1610612744</v>
+      </c>
+      <c r="F578">
+        <v>2024</v>
+      </c>
+      <c r="G578">
+        <v>104</v>
+      </c>
+      <c r="H578">
+        <v>101</v>
+      </c>
+      <c r="I578">
+        <v>28</v>
+      </c>
+      <c r="J578">
+        <v>23</v>
+      </c>
+      <c r="K578">
+        <v>44</v>
+      </c>
+      <c r="L578">
+        <v>46</v>
+      </c>
+      <c r="M578">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="N578">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="O578">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P578">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="Q578">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="R578">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="S578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>672</v>
+      </c>
+      <c r="B579">
+        <v>22400551</v>
+      </c>
+      <c r="C579" t="s">
+        <v>676</v>
+      </c>
+      <c r="D579">
+        <v>1610612745</v>
+      </c>
+      <c r="E579">
+        <v>1610612763</v>
+      </c>
+      <c r="F579">
+        <v>2024</v>
+      </c>
+      <c r="G579">
+        <v>120</v>
+      </c>
+      <c r="H579">
+        <v>118</v>
+      </c>
+      <c r="I579">
+        <v>28</v>
+      </c>
+      <c r="J579">
+        <v>15</v>
+      </c>
+      <c r="K579">
+        <v>40</v>
+      </c>
+      <c r="L579">
+        <v>31</v>
+      </c>
+      <c r="M579">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="N579">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="O579">
+        <v>0.71</v>
+      </c>
+      <c r="P579">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q579">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="R579">
+        <v>0.438</v>
+      </c>
+      <c r="S579">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>672</v>
+      </c>
+      <c r="B580">
+        <v>22400552</v>
+      </c>
+      <c r="C580" t="s">
+        <v>677</v>
+      </c>
+      <c r="D580">
+        <v>1610612747</v>
+      </c>
+      <c r="E580">
+        <v>1610612759</v>
+      </c>
+      <c r="F580">
+        <v>2024</v>
+      </c>
+      <c r="G580">
+        <v>102</v>
+      </c>
+      <c r="H580">
+        <v>126</v>
+      </c>
+      <c r="I580">
+        <v>24</v>
+      </c>
+      <c r="J580">
+        <v>30</v>
+      </c>
+      <c r="K580">
+        <v>40</v>
+      </c>
+      <c r="L580">
+        <v>41</v>
+      </c>
+      <c r="M580">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="N580">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="O580">
+        <v>0.625</v>
+      </c>
+      <c r="P580">
+        <v>0.85</v>
+      </c>
+      <c r="Q580">
+        <v>0.318</v>
+      </c>
+      <c r="R580">
+        <v>0.371</v>
+      </c>
+      <c r="S580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>672</v>
+      </c>
+      <c r="B581">
+        <v>22400553</v>
+      </c>
+      <c r="C581" t="s">
+        <v>678</v>
+      </c>
+      <c r="D581">
+        <v>1610612746</v>
+      </c>
+      <c r="E581">
+        <v>1610612748</v>
+      </c>
+      <c r="F581">
+        <v>2024</v>
+      </c>
+      <c r="G581">
+        <v>109</v>
+      </c>
+      <c r="H581">
+        <v>98</v>
+      </c>
+      <c r="I581">
+        <v>28</v>
+      </c>
+      <c r="J581">
+        <v>22</v>
+      </c>
+      <c r="K581">
+        <v>48</v>
+      </c>
+      <c r="L581">
+        <v>49</v>
+      </c>
+      <c r="M581">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="N581">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="O581">
+        <v>0.6</v>
+      </c>
+      <c r="P581">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="Q581">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="R581">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="S581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>679</v>
+      </c>
+      <c r="B582">
+        <v>22400554</v>
+      </c>
+      <c r="C582" t="s">
+        <v>680</v>
+      </c>
+      <c r="D582">
+        <v>1610612754</v>
+      </c>
+      <c r="E582">
+        <v>1610612739</v>
+      </c>
+      <c r="F582">
+        <v>2024</v>
+      </c>
+      <c r="G582">
+        <v>117</v>
+      </c>
+      <c r="H582">
+        <v>127</v>
+      </c>
+      <c r="I582">
+        <v>30</v>
+      </c>
+      <c r="J582">
+        <v>25</v>
+      </c>
+      <c r="K582">
+        <v>37</v>
+      </c>
+      <c r="L582">
+        <v>49</v>
+      </c>
+      <c r="M582">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="N582">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="O582">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="P582">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="Q582">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="R582">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="S582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>679</v>
+      </c>
+      <c r="B583">
+        <v>22400555</v>
+      </c>
+      <c r="C583" t="s">
+        <v>681</v>
+      </c>
+      <c r="D583">
+        <v>1610612755</v>
+      </c>
+      <c r="E583">
+        <v>1610612760</v>
+      </c>
+      <c r="F583">
+        <v>2024</v>
+      </c>
+      <c r="G583">
+        <v>102</v>
+      </c>
+      <c r="H583">
+        <v>118</v>
+      </c>
+      <c r="I583">
+        <v>23</v>
+      </c>
+      <c r="J583">
+        <v>32</v>
+      </c>
+      <c r="K583">
+        <v>35</v>
+      </c>
+      <c r="L583">
+        <v>38</v>
+      </c>
+      <c r="M583">
+        <v>0.44</v>
+      </c>
+      <c r="N583">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="O583">
+        <v>0.75</v>
+      </c>
+      <c r="P583">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="Q583">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="R583">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="S583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>679</v>
+      </c>
+      <c r="B584">
+        <v>22400556</v>
+      </c>
+      <c r="C584" t="s">
+        <v>682</v>
+      </c>
+      <c r="D584">
+        <v>1610612737</v>
+      </c>
+      <c r="E584">
+        <v>1610612756</v>
+      </c>
+      <c r="F584">
+        <v>2024</v>
+      </c>
+      <c r="G584">
+        <v>122</v>
+      </c>
+      <c r="H584">
+        <v>117</v>
+      </c>
+      <c r="I584">
+        <v>22</v>
+      </c>
+      <c r="J584">
+        <v>28</v>
+      </c>
+      <c r="K584">
+        <v>54</v>
+      </c>
+      <c r="L584">
+        <v>37</v>
+      </c>
+      <c r="M584">
+        <v>0.439</v>
+      </c>
+      <c r="N584">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="O584">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="P584">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q584">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="R584">
+        <v>0.371</v>
+      </c>
+      <c r="S584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>679</v>
+      </c>
+      <c r="B585">
+        <v>22400557</v>
+      </c>
+      <c r="C585" t="s">
+        <v>683</v>
+      </c>
+      <c r="D585">
+        <v>1610612741</v>
+      </c>
+      <c r="E585">
+        <v>1610612740</v>
+      </c>
+      <c r="F585">
+        <v>2024</v>
+      </c>
+      <c r="G585">
+        <v>113</v>
+      </c>
+      <c r="H585">
+        <v>119</v>
+      </c>
+      <c r="I585">
+        <v>31</v>
+      </c>
+      <c r="J585">
+        <v>32</v>
+      </c>
+      <c r="K585">
+        <v>57</v>
+      </c>
+      <c r="L585">
+        <v>46</v>
+      </c>
+      <c r="M585">
+        <v>0.441</v>
+      </c>
+      <c r="N585">
+        <v>0.438</v>
+      </c>
+      <c r="O585">
+        <v>0.75</v>
+      </c>
+      <c r="P585">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="Q585">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="R585">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="S585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>679</v>
+      </c>
+      <c r="B586">
+        <v>22400558</v>
+      </c>
+      <c r="C586" t="s">
+        <v>684</v>
+      </c>
+      <c r="D586">
+        <v>1610612749</v>
+      </c>
+      <c r="E586">
+        <v>1610612758</v>
+      </c>
+      <c r="F586">
+        <v>2024</v>
+      </c>
+      <c r="G586">
+        <v>130</v>
+      </c>
+      <c r="H586">
+        <v>115</v>
+      </c>
+      <c r="I586">
+        <v>32</v>
+      </c>
+      <c r="J586">
+        <v>25</v>
+      </c>
+      <c r="K586">
+        <v>52</v>
+      </c>
+      <c r="L586">
+        <v>45</v>
+      </c>
+      <c r="M586">
+        <v>0.495</v>
+      </c>
+      <c r="N586">
+        <v>0.442</v>
+      </c>
+      <c r="O586">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="P586">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="Q586">
+        <v>0.378</v>
+      </c>
+      <c r="R586">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="S586">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>679</v>
+      </c>
+      <c r="B587">
+        <v>22400559</v>
+      </c>
+      <c r="C587" t="s">
+        <v>685</v>
+      </c>
+      <c r="D587">
+        <v>1610612742</v>
+      </c>
+      <c r="E587">
+        <v>1610612743</v>
+      </c>
+      <c r="F587">
+        <v>2024</v>
+      </c>
+      <c r="G587">
+        <v>99</v>
+      </c>
+      <c r="H587">
+        <v>118</v>
+      </c>
+      <c r="I587">
+        <v>27</v>
+      </c>
+      <c r="J587">
+        <v>28</v>
+      </c>
+      <c r="K587">
+        <v>30</v>
+      </c>
+      <c r="L587">
+        <v>51</v>
+      </c>
+      <c r="M587">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="N587">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="O587">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="P587">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="Q587">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="R587">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="S587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>679</v>
+      </c>
+      <c r="B588">
+        <v>22400560</v>
+      </c>
+      <c r="C588" t="s">
+        <v>686</v>
+      </c>
+      <c r="D588">
+        <v>1610612757</v>
+      </c>
+      <c r="E588">
+        <v>1610612751</v>
+      </c>
+      <c r="F588">
+        <v>2024</v>
+      </c>
+      <c r="G588">
+        <v>114</v>
+      </c>
+      <c r="H588">
+        <v>132</v>
+      </c>
+      <c r="I588">
+        <v>20</v>
+      </c>
+      <c r="J588">
+        <v>36</v>
+      </c>
+      <c r="K588">
+        <v>38</v>
+      </c>
+      <c r="L588">
+        <v>44</v>
+      </c>
+      <c r="M588">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="N588">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="O588">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="P588">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="Q588">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="R588">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="S588">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/model/data/games.xlsx
+++ b/model/data/games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S761"/>
+  <dimension ref="A1:S768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48405,6 +48405,447 @@
         <v>0</v>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>22400734</v>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>20250207/SASCHA</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="E762" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="F762" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G762" t="n">
+        <v>117</v>
+      </c>
+      <c r="H762" t="n">
+        <v>116</v>
+      </c>
+      <c r="I762" t="n">
+        <v>33</v>
+      </c>
+      <c r="J762" t="n">
+        <v>25</v>
+      </c>
+      <c r="K762" t="n">
+        <v>53</v>
+      </c>
+      <c r="L762" t="n">
+        <v>38</v>
+      </c>
+      <c r="M762" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="N762" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="O762" t="n">
+        <v>1</v>
+      </c>
+      <c r="P762" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q762" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="R762" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="S762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>22400735</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>20250207/CLEWAS</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>1610612764</v>
+      </c>
+      <c r="E763" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="F763" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G763" t="n">
+        <v>124</v>
+      </c>
+      <c r="H763" t="n">
+        <v>134</v>
+      </c>
+      <c r="I763" t="n">
+        <v>25</v>
+      </c>
+      <c r="J763" t="n">
+        <v>32</v>
+      </c>
+      <c r="K763" t="n">
+        <v>40</v>
+      </c>
+      <c r="L763" t="n">
+        <v>46</v>
+      </c>
+      <c r="M763" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="N763" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="O763" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P763" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="Q763" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R763" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="S763" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>22400736</v>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>20250207/MILATL</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>1610612737</v>
+      </c>
+      <c r="E764" t="n">
+        <v>1610612749</v>
+      </c>
+      <c r="F764" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G764" t="n">
+        <v>115</v>
+      </c>
+      <c r="H764" t="n">
+        <v>110</v>
+      </c>
+      <c r="I764" t="n">
+        <v>29</v>
+      </c>
+      <c r="J764" t="n">
+        <v>28</v>
+      </c>
+      <c r="K764" t="n">
+        <v>52</v>
+      </c>
+      <c r="L764" t="n">
+        <v>43</v>
+      </c>
+      <c r="M764" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="N764" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="O764" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="P764" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q764" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R764" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S764" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>22400737</v>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>20250207/MIABKN</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="E765" t="n">
+        <v>1610612748</v>
+      </c>
+      <c r="F765" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G765" t="n">
+        <v>102</v>
+      </c>
+      <c r="H765" t="n">
+        <v>86</v>
+      </c>
+      <c r="I765" t="n">
+        <v>17</v>
+      </c>
+      <c r="J765" t="n">
+        <v>23</v>
+      </c>
+      <c r="K765" t="n">
+        <v>57</v>
+      </c>
+      <c r="L765" t="n">
+        <v>39</v>
+      </c>
+      <c r="M765" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="N765" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="O765" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="P765" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q765" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R765" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S765" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>22400738</v>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>20250207/PHIDET</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="E766" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="F766" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G766" t="n">
+        <v>125</v>
+      </c>
+      <c r="H766" t="n">
+        <v>112</v>
+      </c>
+      <c r="I766" t="n">
+        <v>32</v>
+      </c>
+      <c r="J766" t="n">
+        <v>26</v>
+      </c>
+      <c r="K766" t="n">
+        <v>56</v>
+      </c>
+      <c r="L766" t="n">
+        <v>38</v>
+      </c>
+      <c r="M766" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="N766" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="O766" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="P766" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q766" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="R766" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="S766" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>22400739</v>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>20250207/TOROKC</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="E767" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="F767" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G767" t="n">
+        <v>121</v>
+      </c>
+      <c r="H767" t="n">
+        <v>109</v>
+      </c>
+      <c r="I767" t="n">
+        <v>26</v>
+      </c>
+      <c r="J767" t="n">
+        <v>31</v>
+      </c>
+      <c r="K767" t="n">
+        <v>44</v>
+      </c>
+      <c r="L767" t="n">
+        <v>42</v>
+      </c>
+      <c r="M767" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="N767" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="O767" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="P767" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="Q767" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="R767" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="S767" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2025-02-07T00:00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>22400740</v>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>20250207/UTAPHX</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>1610612756</v>
+      </c>
+      <c r="E768" t="n">
+        <v>1610612762</v>
+      </c>
+      <c r="F768" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G768" t="n">
+        <v>135</v>
+      </c>
+      <c r="H768" t="n">
+        <v>127</v>
+      </c>
+      <c r="I768" t="n">
+        <v>31</v>
+      </c>
+      <c r="J768" t="n">
+        <v>29</v>
+      </c>
+      <c r="K768" t="n">
+        <v>49</v>
+      </c>
+      <c r="L768" t="n">
+        <v>63</v>
+      </c>
+      <c r="M768" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="N768" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O768" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="P768" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q768" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="R768" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="S768" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
